--- a/db/NCCU-151-ClassmateRenuion.xlsx
+++ b/db/NCCU-151-ClassmateRenuion.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="253">
   <si>
     <t>No</t>
   </si>
@@ -4063,6 +4063,84 @@
     您的瀏覽器不支援影片播放。
   &lt;/video&gt;
 &lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>同學會聚餐</t>
+  </si>
+  <si>
+    <t>張誠俊自美返台
+1. 孫全玉2. 張誠俊3王貽媺
+4. 韓永健5. 王台鳯6.李素美
+7.施紫玲8.周成波9.呂和美
+10.黎銀妹</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;2026年1月9日   天氣睛寒冷&lt;/p&gt;
+&lt;p&gt;今年（2026）元月開春第一炮，張誠俊夫婦自美返台。班長邀請同學聚餐，地點選在艾美酒店探索廚房。此地點在2025年年底環境內部改裝並且美食升級。大受客戶好評推薦。&lt;/p&gt;
+&lt;p&gt;今天出席同學計有十位。非常難得請到誠俊好友政大同屆校友統計系畢業韓永健自紐約返台一同出席參加。&lt;/p&gt;
+&lt;p&gt;大家在環境氣氛地方聚餐，享受美食饗宴，並且品嚐多種調酒🍸。&lt;/p&gt;
+&lt;p&gt;祝福大家身體健康、平安萬事如意！&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;div id="carouselExampleIndicators-26-0109-1" class="carousel slide img-fluid" data-ride="carousel"&gt;
+	&lt;ol class="carousel-indicators"&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="01" class="active"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="02"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="03"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="04"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="05"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="06"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="07"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="08"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="09"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="10"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="11"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="12"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="13"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="14"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="15"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="16"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="17"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="18"&gt;&lt;/li&gt;
+		&lt;li data-target="#carouselExampleIndicators" data-slide-to="19"&gt;&lt;/li&gt;
+	&lt;/ol&gt;
+	&lt;div class="carousel-inner"&gt;
+		&lt;div class="carousel-item active"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-01.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-02.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-03.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-04.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-05.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-06.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;	
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-07.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-08.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-09.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-10.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-11.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-12.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-13.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-14.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-15.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-16.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-17.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-18.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;
+		&lt;div class="carousel-item"&gt;&lt;img src="fig/NCCU-14-ClassRenuion/NCCU-1402-2026-0109-19.jpg" class="d-block w-100" alt="..."&gt;&lt;/div&gt;			
+	&lt;/div&gt;
+	&lt;a class="carousel-control-prev" href="#carouselExampleIndicators-20-0109-1" role="button"	data-slide="prev"&gt;
+		&lt;span class="carousel-control-prev-icon" aria-hidden="true"&gt;&lt;/span&gt;
+		&lt;span class="sr-only"&gt;Previous&lt;/span&gt;
+	&lt;/a&gt;
+	&lt;a class="carousel-control-next" href="#carouselExampleIndicators-26-0109-1" role="button" data-slide="next"&gt;
+		&lt;span class="carousel-control-next-icon" aria-hidden="true"&gt;&lt;/span&gt;
+		&lt;span class="sr-only"&gt;Next&lt;/span&gt;
+	&lt;/a&gt;
+&lt;/div&gt;
+</t>
   </si>
 </sst>
 </file>
@@ -5236,7 +5314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="19" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.8516" style="1" customWidth="1"/>
@@ -6444,6 +6522,32 @@
         <v>246</v>
       </c>
     </row>
+    <row r="50" ht="759" customHeight="1">
+      <c r="A50" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C50" t="s" s="6">
+        <v>249</v>
+      </c>
+      <c r="D50" s="4">
+        <v>46031</v>
+      </c>
+      <c r="E50" t="s" s="6">
+        <v>63</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
